--- a/docs/tables/summary_all_objects_accuracy_f1_EN.xlsx
+++ b/docs/tables/summary_all_objects_accuracy_f1_EN.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:Z25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -457,11 +457,23 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="60" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -512,25 +524,85 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>alignment RMSE (mm)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>points within 3cm (%)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>accuracy@3cm (%)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>completeness@3cm (%)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>F1@3cm (%)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy@5cm (%)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>completeness@5cm (%)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>F1@5cm (%)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy@10cm (%)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>completeness@10cm (%)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>F1@10cm (%)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ΔF1@10-3cm (pp)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>raw points</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>matched points (1cm voxel)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>raw/matched ratio</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>DBSCAN mode</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>reference note</t>
         </is>
@@ -571,20 +643,56 @@
         <v>1.31</v>
       </c>
       <c r="J2" s="4" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="L2" s="4" t="n">
         <v>44.6</v>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="M2" s="4" t="n">
         <v>79.2</v>
       </c>
-      <c r="L2" s="5" t="n">
+      <c r="N2" s="5" t="n">
         <v>57.1</v>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="O2" s="4" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="Q2" s="5" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="T2" s="4" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="U2" s="4" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="V2" s="4" t="n">
+        <v>1150918</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>458520</v>
+      </c>
+      <c r="X2" s="4" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
         <is>
           <t>ft10/eps3/mp5</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr">
+      <c r="Z2" s="6" t="inlineStr">
         <is>
           <t>incomplete reference: the bus stop's far side (away from the road) wasn't scanned; part of the reference is a merge of 2 scans that don't align perfectly in places</t>
         </is>
@@ -603,13 +711,49 @@
         <v>0.71</v>
       </c>
       <c r="J3" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="K3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="L3" t="n">
         <v>28.6</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>96.40000000000001</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>44.1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="P3" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="R3" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="S3" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="T3" s="7" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="U3" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="V3" t="n">
+        <v>6995057</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2432352</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.88</v>
       </c>
     </row>
     <row r="4">
@@ -625,13 +769,49 @@
         <v>4.03</v>
       </c>
       <c r="J4" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="K4" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="L4" t="n">
         <v>56.8</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>39</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>46.3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="R4" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="S4" t="n">
+        <v>93</v>
+      </c>
+      <c r="T4" t="n">
+        <v>96</v>
+      </c>
+      <c r="U4" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="V4" t="n">
+        <v>624826</v>
+      </c>
+      <c r="W4" t="n">
+        <v>118844</v>
+      </c>
+      <c r="X4" t="n">
+        <v>5.26</v>
       </c>
     </row>
     <row r="5">
@@ -647,13 +827,49 @@
         <v>3.7</v>
       </c>
       <c r="J5" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="K5" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="L5" t="n">
         <v>48.3</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>40.5</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>44.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="R5" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="T5" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="V5" t="n">
+        <v>789125</v>
+      </c>
+      <c r="W5" t="n">
+        <v>139982</v>
+      </c>
+      <c r="X5" t="n">
+        <v>5.64</v>
       </c>
     </row>
     <row r="6">
@@ -685,26 +901,62 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.88</v>
+        <v>1.61</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>0.64</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>67.2</v>
+        <v>16.09</v>
       </c>
       <c r="K6" s="4" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="M6" s="4" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="L6" s="5" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>ft7/eps3/mp5</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
+      <c r="N6" s="5" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>734656</v>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>70153</v>
+      </c>
+      <c r="X6" s="4" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>ft5/eps2/mp3</t>
+        </is>
+      </c>
+      <c r="Z6" s="6" t="inlineStr">
         <is>
           <t>incomplete reference: only the upper ~2/3 of the pole height and one side were scanned — comparison is only valid in that region (not a scale/rotation error)</t>
         </is>
@@ -717,19 +969,55 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3.66</v>
+        <v>2.84</v>
       </c>
       <c r="I7" t="n">
         <v>0.63</v>
       </c>
       <c r="J7" t="n">
-        <v>39.1</v>
+        <v>19.77</v>
       </c>
       <c r="K7" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>54</v>
+      </c>
+      <c r="M7" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="L7" t="n">
-        <v>56.1</v>
+      <c r="N7" t="n">
+        <v>70</v>
+      </c>
+      <c r="O7" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="P7" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="R7" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="S7" t="n">
+        <v>100</v>
+      </c>
+      <c r="T7" t="n">
+        <v>100</v>
+      </c>
+      <c r="U7" t="n">
+        <v>30</v>
+      </c>
+      <c r="V7" t="n">
+        <v>3334257</v>
+      </c>
+      <c r="W7" t="n">
+        <v>161957</v>
+      </c>
+      <c r="X7" t="n">
+        <v>20.59</v>
       </c>
     </row>
     <row r="8">
@@ -739,19 +1027,55 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="I8" t="n">
         <v>0.58</v>
       </c>
       <c r="J8" t="n">
-        <v>68.59999999999999</v>
+        <v>14.82</v>
       </c>
       <c r="K8" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="M8" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="L8" t="n">
-        <v>77.7</v>
+      <c r="N8" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="R8" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="S8" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="U8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1123433</v>
+      </c>
+      <c r="W8" t="n">
+        <v>36738</v>
+      </c>
+      <c r="X8" t="n">
+        <v>30.58</v>
       </c>
     </row>
     <row r="9">
@@ -761,19 +1085,55 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="I9" t="n">
         <v>0.91</v>
       </c>
       <c r="J9" t="n">
-        <v>61.7</v>
+        <v>15.7</v>
       </c>
       <c r="K9" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M9" t="n">
         <v>86.3</v>
       </c>
-      <c r="L9" t="n">
-        <v>72</v>
+      <c r="N9" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="O9" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="R9" t="n">
+        <v>100</v>
+      </c>
+      <c r="S9" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="T9" t="n">
+        <v>99</v>
+      </c>
+      <c r="U9" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1064834</v>
+      </c>
+      <c r="W9" t="n">
+        <v>37804</v>
+      </c>
+      <c r="X9" t="n">
+        <v>28.17</v>
       </c>
     </row>
     <row r="10">
@@ -805,26 +1165,62 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>1.48</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>65.90000000000001</v>
+        <v>19.55</v>
       </c>
       <c r="K10" s="4" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="M10" s="4" t="n">
         <v>71.7</v>
       </c>
-      <c r="L10" s="5" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>ft5/eps2/mp4</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="inlineStr">
+      <c r="N10" s="5" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="U10" s="4" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>804316</v>
+      </c>
+      <c r="W10" s="4" t="n">
+        <v>136786</v>
+      </c>
+      <c r="X10" s="4" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>ft5/eps3/mp2</t>
+        </is>
+      </c>
+      <c r="Z10" s="6" t="inlineStr">
         <is>
           <t>incomplete reference: the bench's backrest (rear side) and legs are missing</t>
         </is>
@@ -837,19 +1233,55 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="I11" t="n">
         <v>1.11</v>
       </c>
       <c r="J11" t="n">
-        <v>55.5</v>
+        <v>20.86</v>
       </c>
       <c r="K11" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="M11" t="n">
         <v>84.5</v>
       </c>
-      <c r="L11" t="n">
-        <v>67</v>
+      <c r="N11" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="Q11" s="7" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="S11" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="T11" s="7" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6726594</v>
+      </c>
+      <c r="W11" t="n">
+        <v>359926</v>
+      </c>
+      <c r="X11" t="n">
+        <v>18.69</v>
       </c>
     </row>
     <row r="12">
@@ -865,13 +1297,49 @@
         <v>1.69</v>
       </c>
       <c r="J12" t="n">
-        <v>66.5</v>
+        <v>19.87</v>
       </c>
       <c r="K12" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="M12" t="n">
         <v>67.2</v>
       </c>
-      <c r="L12" t="n">
-        <v>66.8</v>
+      <c r="N12" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="O12" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="P12" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>100</v>
+      </c>
+      <c r="S12" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1520520</v>
+      </c>
+      <c r="W12" t="n">
+        <v>115064</v>
+      </c>
+      <c r="X12" t="n">
+        <v>13.21</v>
       </c>
     </row>
     <row r="13">
@@ -887,13 +1355,49 @@
         <v>2.8</v>
       </c>
       <c r="J13" t="n">
-        <v>57.2</v>
+        <v>21.7</v>
       </c>
       <c r="K13" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="M13" t="n">
         <v>54.6</v>
       </c>
-      <c r="L13" t="n">
-        <v>55.8</v>
+      <c r="N13" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="O13" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="P13" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>100</v>
+      </c>
+      <c r="S13" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="T13" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="U13" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1462675</v>
+      </c>
+      <c r="W13" t="n">
+        <v>103983</v>
+      </c>
+      <c r="X13" t="n">
+        <v>14.07</v>
       </c>
     </row>
     <row r="14">
@@ -931,20 +1435,56 @@
         <v>0.61</v>
       </c>
       <c r="J14" s="4" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="L14" s="4" t="n">
         <v>91.3</v>
       </c>
-      <c r="K14" s="4" t="n">
+      <c r="M14" s="4" t="n">
         <v>97</v>
       </c>
-      <c r="L14" s="5" t="n">
+      <c r="N14" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="O14" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="S14" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="U14" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>533608</v>
+      </c>
+      <c r="W14" s="4" t="n">
+        <v>14002</v>
+      </c>
+      <c r="X14" s="4" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
         <is>
           <t>ft5/eps2/mp3</t>
         </is>
       </c>
-      <c r="N14" s="6" t="inlineStr">
+      <c r="Z14" s="6" t="inlineStr">
         <is>
           <t>incomplete reference: only one side was scanned (~90° sector missing) — the missing side is handled via gap detection (DBSCAN)</t>
         </is>
@@ -963,13 +1503,49 @@
         <v>0.63</v>
       </c>
       <c r="J15" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="K15" t="n">
+        <v>64</v>
+      </c>
+      <c r="L15" t="n">
         <v>86.40000000000001</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>97</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>91.40000000000001</v>
+      </c>
+      <c r="O15" t="n">
+        <v>100</v>
+      </c>
+      <c r="P15" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q15" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="R15" t="n">
+        <v>100</v>
+      </c>
+      <c r="S15" t="n">
+        <v>100</v>
+      </c>
+      <c r="T15" t="n">
+        <v>100</v>
+      </c>
+      <c r="U15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3697595</v>
+      </c>
+      <c r="W15" t="n">
+        <v>28592</v>
+      </c>
+      <c r="X15" t="n">
+        <v>129.32</v>
       </c>
     </row>
     <row r="16">
@@ -985,13 +1561,49 @@
         <v>1.21</v>
       </c>
       <c r="J16" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="K16" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="L16" t="n">
         <v>87.5</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>83.8</v>
+      </c>
+      <c r="O16" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="P16" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="S16" t="n">
+        <v>100</v>
+      </c>
+      <c r="T16" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="U16" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>214105</v>
+      </c>
+      <c r="W16" t="n">
+        <v>6021</v>
+      </c>
+      <c r="X16" t="n">
+        <v>35.56</v>
       </c>
     </row>
     <row r="17">
@@ -1007,13 +1619,49 @@
         <v>0.89</v>
       </c>
       <c r="J17" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="K17" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="L17" t="n">
         <v>88.3</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>89.90000000000001</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>89.09999999999999</v>
+      </c>
+      <c r="O17" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="P17" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>100</v>
+      </c>
+      <c r="S17" t="n">
+        <v>100</v>
+      </c>
+      <c r="T17" t="n">
+        <v>100</v>
+      </c>
+      <c r="U17" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="V17" t="n">
+        <v>308184</v>
+      </c>
+      <c r="W17" t="n">
+        <v>7106</v>
+      </c>
+      <c r="X17" t="n">
+        <v>43.37</v>
       </c>
     </row>
     <row r="18">
@@ -1051,20 +1699,56 @@
         <v>1.32</v>
       </c>
       <c r="J18" s="4" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="K18" s="4" t="n">
         <v>44.5</v>
       </c>
-      <c r="K18" s="4" t="n">
+      <c r="L18" s="4" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="M18" s="4" t="n">
         <v>88.8</v>
       </c>
-      <c r="L18" s="4" t="n">
+      <c r="N18" s="4" t="n">
         <v>59.3</v>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="O18" s="4" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="S18" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="U18" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>177102</v>
+      </c>
+      <c r="W18" s="4" t="n">
+        <v>46577</v>
+      </c>
+      <c r="X18" s="4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
         <is>
           <t>no DBSCAN</t>
         </is>
       </c>
-      <c r="N18" s="6" t="inlineStr">
+      <c r="Z18" s="6" t="inlineStr">
         <is>
           <t>full reference</t>
         </is>
@@ -1083,13 +1767,49 @@
         <v>1.17</v>
       </c>
       <c r="J19" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="K19" t="n">
         <v>12.3</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="M19" t="n">
         <v>96</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>21.8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="P19" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>100</v>
+      </c>
+      <c r="T19" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="V19" t="n">
+        <v>293168</v>
+      </c>
+      <c r="W19" t="n">
+        <v>152549</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.92</v>
       </c>
     </row>
     <row r="20">
@@ -1105,13 +1825,49 @@
         <v>1.23</v>
       </c>
       <c r="J20" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="K20" t="n">
         <v>96.59999999999999</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="M20" t="n">
         <v>82.90000000000001</v>
       </c>
-      <c r="L20" s="7" t="n">
+      <c r="N20" s="7" t="n">
         <v>89.2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="P20" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="Q20" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="R20" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="S20" t="n">
+        <v>98</v>
+      </c>
+      <c r="T20" s="7" t="n">
+        <v>99</v>
+      </c>
+      <c r="U20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V20" t="n">
+        <v>133185</v>
+      </c>
+      <c r="W20" t="n">
+        <v>18583</v>
+      </c>
+      <c r="X20" t="n">
+        <v>7.17</v>
       </c>
     </row>
     <row r="21">
@@ -1127,13 +1883,49 @@
         <v>1.65</v>
       </c>
       <c r="J21" t="n">
+        <v>13</v>
+      </c>
+      <c r="K21" t="n">
         <v>91.7</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="M21" t="n">
         <v>75.2</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>82.59999999999999</v>
+      </c>
+      <c r="O21" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="P21" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="R21" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="S21" t="n">
+        <v>89</v>
+      </c>
+      <c r="T21" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="U21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="V21" t="n">
+        <v>59502</v>
+      </c>
+      <c r="W21" t="n">
+        <v>10543</v>
+      </c>
+      <c r="X21" t="n">
+        <v>5.64</v>
       </c>
     </row>
     <row r="22">
@@ -1171,20 +1963,56 @@
         <v>1.3</v>
       </c>
       <c r="J22" s="4" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="K22" s="4" t="n">
         <v>28.6</v>
       </c>
-      <c r="K22" s="4" t="n">
+      <c r="L22" s="4" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="M22" s="4" t="n">
         <v>83.3</v>
       </c>
-      <c r="L22" s="4" t="n">
+      <c r="N22" s="4" t="n">
         <v>42.6</v>
       </c>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="O22" s="4" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="S22" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="U22" s="4" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>569403</v>
+      </c>
+      <c r="W22" s="4" t="n">
+        <v>130311</v>
+      </c>
+      <c r="X22" s="4" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
         <is>
           <t>no DBSCAN</t>
         </is>
       </c>
-      <c r="N22" s="6" t="inlineStr">
+      <c r="Z22" s="6" t="inlineStr">
         <is>
           <t>full reference</t>
         </is>
@@ -1203,13 +2031,49 @@
         <v>0.58</v>
       </c>
       <c r="J23" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="K23" t="n">
         <v>35.5</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="M23" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>52.4</v>
+      </c>
+      <c r="O23" t="n">
+        <v>54</v>
+      </c>
+      <c r="P23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="R23" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="S23" t="n">
+        <v>100</v>
+      </c>
+      <c r="T23" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="U23" t="n">
+        <v>37</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2881563</v>
+      </c>
+      <c r="W23" t="n">
+        <v>322936</v>
+      </c>
+      <c r="X23" t="n">
+        <v>8.92</v>
       </c>
     </row>
     <row r="24">
@@ -1225,13 +2089,49 @@
         <v>1.88</v>
       </c>
       <c r="J24" t="n">
+        <v>17.77</v>
+      </c>
+      <c r="K24" t="n">
         <v>58.8</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="M24" t="n">
         <v>78.40000000000001</v>
       </c>
-      <c r="L24" s="7" t="n">
+      <c r="N24" s="7" t="n">
         <v>67.2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="P24" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="Q24" s="7" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="R24" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="S24" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="T24" s="7" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="U24" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="V24" t="n">
+        <v>327676</v>
+      </c>
+      <c r="W24" t="n">
+        <v>29266</v>
+      </c>
+      <c r="X24" t="n">
+        <v>11.2</v>
       </c>
     </row>
     <row r="25">
@@ -1247,13 +2147,49 @@
         <v>2.16</v>
       </c>
       <c r="J25" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="K25" t="n">
         <v>52.7</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="M25" t="n">
         <v>64.3</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>58</v>
+      </c>
+      <c r="O25" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="P25" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="S25" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="T25" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="U25" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="V25" t="n">
+        <v>261293</v>
+      </c>
+      <c r="W25" t="n">
+        <v>23147</v>
+      </c>
+      <c r="X25" t="n">
+        <v>11.29</v>
       </c>
     </row>
   </sheetData>
@@ -1263,46 +2199,46 @@
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="E14:E17"/>
     <mergeCell ref="D22:D25"/>
-    <mergeCell ref="N22:N25"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="D6:D9"/>
     <mergeCell ref="F6:F9"/>
-    <mergeCell ref="M2:M5"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="C10:C13"/>
     <mergeCell ref="D2:D5"/>
-    <mergeCell ref="M10:M13"/>
     <mergeCell ref="E10:E13"/>
     <mergeCell ref="B14:B17"/>
-    <mergeCell ref="N18:N21"/>
+    <mergeCell ref="Y14:Y17"/>
     <mergeCell ref="C22:C25"/>
     <mergeCell ref="F18:F21"/>
+    <mergeCell ref="Z22:Z25"/>
     <mergeCell ref="C18:C21"/>
-    <mergeCell ref="M22:M25"/>
+    <mergeCell ref="Z18:Z21"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="F2:F5"/>
     <mergeCell ref="E6:E9"/>
-    <mergeCell ref="N2:N5"/>
-    <mergeCell ref="M6:M9"/>
+    <mergeCell ref="Y2:Y5"/>
+    <mergeCell ref="Z2:Z5"/>
+    <mergeCell ref="Y10:Y13"/>
     <mergeCell ref="B10:B13"/>
-    <mergeCell ref="N14:N17"/>
+    <mergeCell ref="Y6:Y9"/>
     <mergeCell ref="A18:A21"/>
     <mergeCell ref="F22:F25"/>
+    <mergeCell ref="Z14:Z17"/>
     <mergeCell ref="D18:D21"/>
-    <mergeCell ref="M18:M21"/>
+    <mergeCell ref="Y22:Y25"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="C2:C5"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="E2:E5"/>
     <mergeCell ref="A14:A17"/>
-    <mergeCell ref="N10:N13"/>
-    <mergeCell ref="N6:N9"/>
+    <mergeCell ref="Z10:Z13"/>
     <mergeCell ref="A10:A13"/>
-    <mergeCell ref="M14:M17"/>
     <mergeCell ref="A22:A25"/>
     <mergeCell ref="D14:D17"/>
     <mergeCell ref="E22:E25"/>
     <mergeCell ref="F14:F17"/>
+    <mergeCell ref="Z6:Z9"/>
+    <mergeCell ref="Y18:Y21"/>
     <mergeCell ref="C6:C9"/>
     <mergeCell ref="D10:D13"/>
     <mergeCell ref="F10:F13"/>

--- a/docs/tables/summary_all_objects_accuracy_f1_EN.xlsx
+++ b/docs/tables/summary_all_objects_accuracy_f1_EN.xlsx
@@ -75,11 +75,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -633,66 +633,66 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>mast3r_ga</t>
+          <t>colmap</t>
         </is>
       </c>
       <c r="H2" s="4" t="n">
-        <v>3.36</v>
+        <v>2.67</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>1.31</v>
+        <v>4.03</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>19.08</v>
+        <v>19.28</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>38.7</v>
+        <v>50.6</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>44.6</v>
+        <v>56.8</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="N2" s="5" t="n">
-        <v>57.1</v>
+        <v>39</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>46.3</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>68.59999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="Q2" s="5" t="n">
-        <v>78.7</v>
+        <v>59.8</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>68.90000000000001</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>99.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>99.2</v>
+        <v>93</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>96</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>42.3</v>
+        <v>49.7</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>1150918</v>
+        <v>624826</v>
       </c>
       <c r="W2" s="4" t="n">
-        <v>458520</v>
+        <v>118844</v>
       </c>
       <c r="X2" s="4" t="n">
-        <v>2.51</v>
+        <v>5.26</v>
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
           <t>ft10/eps3/mp5</t>
         </is>
       </c>
-      <c r="Z2" s="6" t="inlineStr">
+      <c r="Z2" s="5" t="inlineStr">
         <is>
           <t>incomplete reference: the bus stop's far side (away from the road) wasn't scanned; part of the reference is a merge of 2 scans that don't align perfectly in places</t>
         </is>
@@ -701,175 +701,175 @@
     <row r="3">
       <c r="G3" t="inlineStr">
         <is>
-          <t>vggt</t>
+          <t>hloc_colmap</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4.75</v>
+        <v>3.09</v>
       </c>
       <c r="I3" t="n">
-        <v>0.71</v>
+        <v>3.7</v>
       </c>
       <c r="J3" t="n">
-        <v>20.04</v>
+        <v>19.75</v>
       </c>
       <c r="K3" t="n">
-        <v>18.7</v>
+        <v>42.8</v>
       </c>
       <c r="L3" t="n">
-        <v>28.6</v>
+        <v>48.3</v>
       </c>
       <c r="M3" t="n">
-        <v>96.40000000000001</v>
+        <v>40.5</v>
       </c>
       <c r="N3" t="n">
         <v>44.1</v>
       </c>
       <c r="O3" t="n">
-        <v>52.8</v>
+        <v>75.5</v>
       </c>
       <c r="P3" t="n">
-        <v>99.09999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>68.90000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="R3" t="n">
-        <v>99.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="S3" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="T3" s="7" t="n">
-        <v>99.59999999999999</v>
+        <v>91.7</v>
+      </c>
+      <c r="T3" t="n">
+        <v>95.3</v>
       </c>
       <c r="U3" t="n">
-        <v>55.5</v>
+        <v>51.2</v>
       </c>
       <c r="V3" t="n">
-        <v>6995057</v>
+        <v>789125</v>
       </c>
       <c r="W3" t="n">
-        <v>2432352</v>
+        <v>139982</v>
       </c>
       <c r="X3" t="n">
-        <v>2.88</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="4">
       <c r="G4" t="inlineStr">
         <is>
-          <t>colmap</t>
+          <t>mast3r_ga</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.67</v>
+        <v>3.36</v>
       </c>
       <c r="I4" t="n">
-        <v>4.03</v>
+        <v>1.31</v>
       </c>
       <c r="J4" t="n">
-        <v>19.28</v>
+        <v>19.08</v>
       </c>
       <c r="K4" t="n">
-        <v>50.6</v>
+        <v>38.7</v>
       </c>
       <c r="L4" t="n">
-        <v>56.8</v>
+        <v>44.6</v>
       </c>
       <c r="M4" t="n">
-        <v>39</v>
-      </c>
-      <c r="N4" t="n">
-        <v>46.3</v>
+        <v>79.2</v>
+      </c>
+      <c r="N4" s="6" t="n">
+        <v>57.1</v>
       </c>
       <c r="O4" t="n">
-        <v>81.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>68.90000000000001</v>
+        <v>92.2</v>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v>78.7</v>
       </c>
       <c r="R4" t="n">
-        <v>99.09999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>93</v>
+        <v>99.2</v>
       </c>
       <c r="T4" t="n">
-        <v>96</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>49.7</v>
+        <v>42.3</v>
       </c>
       <c r="V4" t="n">
-        <v>624826</v>
+        <v>1150918</v>
       </c>
       <c r="W4" t="n">
-        <v>118844</v>
+        <v>458520</v>
       </c>
       <c r="X4" t="n">
-        <v>5.26</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="5">
       <c r="G5" t="inlineStr">
         <is>
-          <t>hloc_colmap</t>
+          <t>vggt</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3.09</v>
+        <v>4.75</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7</v>
+        <v>0.71</v>
       </c>
       <c r="J5" t="n">
-        <v>19.75</v>
+        <v>20.04</v>
       </c>
       <c r="K5" t="n">
-        <v>42.8</v>
+        <v>18.7</v>
       </c>
       <c r="L5" t="n">
-        <v>48.3</v>
+        <v>28.6</v>
       </c>
       <c r="M5" t="n">
-        <v>40.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N5" t="n">
         <v>44.1</v>
       </c>
       <c r="O5" t="n">
-        <v>75.5</v>
+        <v>52.8</v>
       </c>
       <c r="P5" t="n">
-        <v>66.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>70.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="T5" t="n">
-        <v>95.3</v>
+        <v>99.90000000000001</v>
+      </c>
+      <c r="T5" s="6" t="n">
+        <v>99.59999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>51.2</v>
+        <v>55.5</v>
       </c>
       <c r="V5" t="n">
-        <v>789125</v>
+        <v>6995057</v>
       </c>
       <c r="W5" t="n">
-        <v>139982</v>
+        <v>2432352</v>
       </c>
       <c r="X5" t="n">
-        <v>5.64</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="6">
@@ -897,66 +897,66 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>mast3r_ga</t>
+          <t>colmap</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>16.09</v>
+        <v>14.82</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>42.3</v>
+        <v>40.5</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>79.90000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v>88.5</v>
+        <v>89.40000000000001</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>85.3</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q6" s="5" t="n">
-        <v>100</v>
+        <v>95.2</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>97.40000000000001</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="T6" s="5" t="n">
-        <v>100</v>
+        <v>99.7</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>99.8</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>734656</v>
+        <v>1123433</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>70153</v>
+        <v>36738</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>10.47</v>
+        <v>30.58</v>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>ft5/eps2/mp3</t>
         </is>
       </c>
-      <c r="Z6" s="6" t="inlineStr">
+      <c r="Z6" s="5" t="inlineStr">
         <is>
           <t>incomplete reference: only the upper ~2/3 of the pole height and one side were scanned — comparison is only valid in that region (not a scale/rotation error)</t>
         </is>
@@ -965,175 +965,175 @@
     <row r="7">
       <c r="G7" t="inlineStr">
         <is>
-          <t>vggt</t>
+          <t>hloc_colmap</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.84</v>
+        <v>1.61</v>
       </c>
       <c r="I7" t="n">
-        <v>0.63</v>
+        <v>0.91</v>
       </c>
       <c r="J7" t="n">
-        <v>19.77</v>
+        <v>15.7</v>
       </c>
       <c r="K7" t="n">
-        <v>24.2</v>
+        <v>35.6</v>
       </c>
       <c r="L7" t="n">
-        <v>54</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>99.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="N7" t="n">
-        <v>70</v>
+        <v>80.8</v>
       </c>
       <c r="O7" t="n">
         <v>99.8</v>
       </c>
       <c r="P7" t="n">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>99.90000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U7" t="n">
-        <v>30</v>
+        <v>18.2</v>
       </c>
       <c r="V7" t="n">
-        <v>3334257</v>
+        <v>1064834</v>
       </c>
       <c r="W7" t="n">
-        <v>161957</v>
+        <v>37804</v>
       </c>
       <c r="X7" t="n">
-        <v>20.59</v>
+        <v>28.17</v>
       </c>
     </row>
     <row r="8">
       <c r="G8" t="inlineStr">
         <is>
-          <t>colmap</t>
+          <t>mast3r_ga</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="I8" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="J8" t="n">
-        <v>14.82</v>
+        <v>16.09</v>
       </c>
       <c r="K8" t="n">
-        <v>40.5</v>
+        <v>42.3</v>
       </c>
       <c r="L8" t="n">
-        <v>81.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="N8" t="n">
-        <v>85.3</v>
+        <v>99.09999999999999</v>
+      </c>
+      <c r="N8" s="6" t="n">
+        <v>88.5</v>
       </c>
       <c r="O8" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="P8" t="n">
-        <v>95.2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>97.40000000000001</v>
+        <v>100</v>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v>100</v>
       </c>
       <c r="R8" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="S8" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="T8" t="n">
-        <v>99.8</v>
+        <v>100</v>
+      </c>
+      <c r="T8" s="6" t="n">
+        <v>100</v>
       </c>
       <c r="U8" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1123433</v>
+        <v>734656</v>
       </c>
       <c r="W8" t="n">
-        <v>36738</v>
+        <v>70153</v>
       </c>
       <c r="X8" t="n">
-        <v>30.58</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="9">
       <c r="G9" t="inlineStr">
         <is>
-          <t>hloc_colmap</t>
+          <t>vggt</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1.61</v>
+        <v>2.84</v>
       </c>
       <c r="I9" t="n">
-        <v>0.91</v>
+        <v>0.63</v>
       </c>
       <c r="J9" t="n">
-        <v>15.7</v>
+        <v>19.77</v>
       </c>
       <c r="K9" t="n">
-        <v>35.6</v>
+        <v>24.2</v>
       </c>
       <c r="L9" t="n">
-        <v>75.90000000000001</v>
+        <v>54</v>
       </c>
       <c r="M9" t="n">
-        <v>86.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>80.8</v>
+        <v>70</v>
       </c>
       <c r="O9" t="n">
         <v>99.8</v>
       </c>
       <c r="P9" t="n">
-        <v>92.3</v>
+        <v>100</v>
       </c>
       <c r="Q9" t="n">
-        <v>95.90000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="U9" t="n">
-        <v>18.2</v>
+        <v>30</v>
       </c>
       <c r="V9" t="n">
-        <v>1064834</v>
+        <v>3334257</v>
       </c>
       <c r="W9" t="n">
-        <v>37804</v>
+        <v>161957</v>
       </c>
       <c r="X9" t="n">
-        <v>28.17</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="10">
@@ -1161,66 +1161,66 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>mast3r_ga</t>
+          <t>colmap</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.48</v>
+        <v>1.69</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>19.55</v>
+        <v>19.87</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>66.2</v>
+        <v>66.7</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>68.8</v>
+        <v>67.2</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>66.90000000000001</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>85.40000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>92.09999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="R10" s="4" t="n">
         <v>100</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>97.09999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>98.5</v>
+        <v>91.7</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>29.7</v>
+        <v>24.8</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>804316</v>
+        <v>1520520</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>136786</v>
+        <v>115064</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>5.88</v>
+        <v>13.21</v>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
           <t>ft5/eps3/mp2</t>
         </is>
       </c>
-      <c r="Z10" s="6" t="inlineStr">
+      <c r="Z10" s="5" t="inlineStr">
         <is>
           <t>incomplete reference: the bench's backrest (rear side) and legs are missing</t>
         </is>
@@ -1229,175 +1229,175 @@
     <row r="11">
       <c r="G11" t="inlineStr">
         <is>
-          <t>vggt</t>
+          <t>hloc_colmap</t>
         </is>
       </c>
       <c r="H11" t="n">
         <v>2.81</v>
       </c>
       <c r="I11" t="n">
-        <v>1.11</v>
+        <v>2.8</v>
       </c>
       <c r="J11" t="n">
-        <v>20.86</v>
+        <v>21.7</v>
       </c>
       <c r="K11" t="n">
-        <v>39.5</v>
+        <v>50.5</v>
       </c>
       <c r="L11" t="n">
-        <v>55.8</v>
+        <v>57.3</v>
       </c>
       <c r="M11" t="n">
-        <v>84.5</v>
+        <v>54.6</v>
       </c>
       <c r="N11" t="n">
-        <v>67.2</v>
+        <v>55.9</v>
       </c>
       <c r="O11" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="Q11" s="7" t="n">
-        <v>96.7</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>86.3</v>
       </c>
       <c r="R11" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="S11" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="T11" s="7" t="n">
-        <v>99.7</v>
+        <v>85.40000000000001</v>
+      </c>
+      <c r="T11" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>32.5</v>
+        <v>36.2</v>
       </c>
       <c r="V11" t="n">
-        <v>6726594</v>
+        <v>1462675</v>
       </c>
       <c r="W11" t="n">
-        <v>359926</v>
+        <v>103983</v>
       </c>
       <c r="X11" t="n">
-        <v>18.69</v>
+        <v>14.07</v>
       </c>
     </row>
     <row r="12">
       <c r="G12" t="inlineStr">
         <is>
-          <t>colmap</t>
+          <t>mast3r_ga</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="I12" t="n">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="J12" t="n">
-        <v>19.87</v>
+        <v>19.55</v>
       </c>
       <c r="K12" t="n">
-        <v>56.2</v>
+        <v>56.1</v>
       </c>
       <c r="L12" t="n">
-        <v>66.7</v>
+        <v>66.2</v>
       </c>
       <c r="M12" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="N12" t="n">
-        <v>66.90000000000001</v>
+        <v>71.7</v>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>68.8</v>
       </c>
       <c r="O12" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="P12" t="n">
-        <v>76.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>86.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="R12" t="n">
         <v>100</v>
       </c>
       <c r="S12" t="n">
-        <v>84.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>91.7</v>
+        <v>98.5</v>
       </c>
       <c r="U12" t="n">
-        <v>24.8</v>
+        <v>29.7</v>
       </c>
       <c r="V12" t="n">
-        <v>1520520</v>
+        <v>804316</v>
       </c>
       <c r="W12" t="n">
-        <v>115064</v>
+        <v>136786</v>
       </c>
       <c r="X12" t="n">
-        <v>13.21</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="13">
       <c r="G13" t="inlineStr">
         <is>
-          <t>hloc_colmap</t>
+          <t>vggt</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>2.81</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8</v>
+        <v>1.11</v>
       </c>
       <c r="J13" t="n">
-        <v>21.7</v>
+        <v>20.86</v>
       </c>
       <c r="K13" t="n">
-        <v>50.5</v>
+        <v>39.5</v>
       </c>
       <c r="L13" t="n">
-        <v>57.3</v>
+        <v>55.8</v>
       </c>
       <c r="M13" t="n">
-        <v>54.6</v>
+        <v>84.5</v>
       </c>
       <c r="N13" t="n">
-        <v>55.9</v>
+        <v>67.2</v>
       </c>
       <c r="O13" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="P13" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="R13" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="P13" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="R13" t="n">
-        <v>100</v>
-      </c>
       <c r="S13" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="T13" t="n">
-        <v>92.09999999999999</v>
+        <v>99.40000000000001</v>
+      </c>
+      <c r="T13" s="6" t="n">
+        <v>99.7</v>
       </c>
       <c r="U13" t="n">
-        <v>36.2</v>
+        <v>32.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1462675</v>
+        <v>6726594</v>
       </c>
       <c r="W13" t="n">
-        <v>103983</v>
+        <v>359926</v>
       </c>
       <c r="X13" t="n">
-        <v>14.07</v>
+        <v>18.69</v>
       </c>
     </row>
     <row r="14">
@@ -1425,66 +1425,66 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>mast3r_ga</t>
+          <t>colmap</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.61</v>
+        <v>1.21</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>12.82</v>
+        <v>12.68</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>72.2</v>
+        <v>68.2</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>91.3</v>
+        <v>87.5</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v>94</v>
+        <v>80.40000000000001</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>83.8</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="P14" s="4" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="R14" s="4" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="Q14" s="4" t="n">
+      <c r="S14" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T14" s="4" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="R14" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="S14" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="T14" s="5" t="n">
-        <v>100</v>
-      </c>
       <c r="U14" s="4" t="n">
-        <v>6</v>
+        <v>16.1</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>533608</v>
+        <v>214105</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>14002</v>
+        <v>6021</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>38.11</v>
+        <v>35.56</v>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
           <t>ft5/eps2/mp3</t>
         </is>
       </c>
-      <c r="Z14" s="6" t="inlineStr">
+      <c r="Z14" s="5" t="inlineStr">
         <is>
           <t>incomplete reference: only one side was scanned (~90° sector missing) — the missing side is handled via gap detection (DBSCAN)</t>
         </is>
@@ -1493,38 +1493,38 @@
     <row r="15">
       <c r="G15" t="inlineStr">
         <is>
-          <t>vggt</t>
+          <t>hloc_colmap</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.31</v>
+        <v>0.95</v>
       </c>
       <c r="I15" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="J15" t="n">
-        <v>14.65</v>
+        <v>12.19</v>
       </c>
       <c r="K15" t="n">
-        <v>64</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>86.40000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="M15" t="n">
-        <v>97</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>91.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="P15" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q15" s="7" t="n">
-        <v>100</v>
+        <v>99.3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>99.5</v>
       </c>
       <c r="R15" t="n">
         <v>100</v>
@@ -1532,115 +1532,115 @@
       <c r="S15" t="n">
         <v>100</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T15" s="6" t="n">
         <v>100</v>
       </c>
       <c r="U15" t="n">
-        <v>8.6</v>
+        <v>10.9</v>
       </c>
       <c r="V15" t="n">
-        <v>3697595</v>
+        <v>308184</v>
       </c>
       <c r="W15" t="n">
-        <v>28592</v>
+        <v>7106</v>
       </c>
       <c r="X15" t="n">
-        <v>129.32</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="16">
       <c r="G16" t="inlineStr">
         <is>
-          <t>colmap</t>
+          <t>mast3r_ga</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="I16" t="n">
-        <v>1.21</v>
+        <v>0.61</v>
       </c>
       <c r="J16" t="n">
-        <v>12.68</v>
+        <v>12.82</v>
       </c>
       <c r="K16" t="n">
-        <v>68.2</v>
+        <v>72.2</v>
       </c>
       <c r="L16" t="n">
-        <v>87.5</v>
+        <v>91.3</v>
       </c>
       <c r="M16" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="N16" t="n">
-        <v>83.8</v>
+        <v>97</v>
+      </c>
+      <c r="N16" s="6" t="n">
+        <v>94</v>
       </c>
       <c r="O16" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="P16" t="n">
-        <v>98.90000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>99.3</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="R16" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="S16" t="n">
         <v>100</v>
       </c>
       <c r="T16" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="U16" t="n">
-        <v>16.1</v>
+        <v>6</v>
       </c>
       <c r="V16" t="n">
-        <v>214105</v>
+        <v>533608</v>
       </c>
       <c r="W16" t="n">
-        <v>6021</v>
+        <v>14002</v>
       </c>
       <c r="X16" t="n">
-        <v>35.56</v>
+        <v>38.11</v>
       </c>
     </row>
     <row r="17">
       <c r="G17" t="inlineStr">
         <is>
-          <t>hloc_colmap</t>
+          <t>vggt</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.95</v>
+        <v>1.31</v>
       </c>
       <c r="I17" t="n">
-        <v>0.89</v>
+        <v>0.63</v>
       </c>
       <c r="J17" t="n">
-        <v>12.19</v>
+        <v>14.65</v>
       </c>
       <c r="K17" t="n">
-        <v>69.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="L17" t="n">
-        <v>88.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>89.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="N17" t="n">
-        <v>89.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="P17" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>99.5</v>
+        <v>100</v>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v>100</v>
       </c>
       <c r="R17" t="n">
         <v>100</v>
@@ -1652,16 +1652,16 @@
         <v>100</v>
       </c>
       <c r="U17" t="n">
-        <v>10.9</v>
+        <v>8.6</v>
       </c>
       <c r="V17" t="n">
-        <v>308184</v>
+        <v>3697595</v>
       </c>
       <c r="W17" t="n">
-        <v>7106</v>
+        <v>28592</v>
       </c>
       <c r="X17" t="n">
-        <v>43.37</v>
+        <v>129.32</v>
       </c>
     </row>
     <row r="18">
@@ -1689,66 +1689,66 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>mast3r_ga</t>
+          <t>colmap</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.48</v>
+        <v>0.98</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>16.84</v>
+        <v>11.59</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>44.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>44.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v>59.3</v>
+        <v>82.90000000000001</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>89.2</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>64.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="Q18" s="4" t="n">
-        <v>77.2</v>
+        <v>90.90000000000001</v>
+      </c>
+      <c r="Q18" s="7" t="n">
+        <v>95</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>87.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="T18" s="4" t="n">
-        <v>93.3</v>
+        <v>98</v>
+      </c>
+      <c r="T18" s="7" t="n">
+        <v>99</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>34</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>177102</v>
+        <v>133185</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>46577</v>
+        <v>18583</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>3.8</v>
+        <v>7.17</v>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
           <t>no DBSCAN</t>
         </is>
       </c>
-      <c r="Z18" s="6" t="inlineStr">
+      <c r="Z18" s="5" t="inlineStr">
         <is>
           <t>full reference</t>
         </is>
@@ -1757,175 +1757,175 @@
     <row r="19">
       <c r="G19" t="inlineStr">
         <is>
-          <t>vggt</t>
+          <t>hloc_colmap</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>10.66</v>
+        <v>1.05</v>
       </c>
       <c r="I19" t="n">
-        <v>1.17</v>
+        <v>1.65</v>
       </c>
       <c r="J19" t="n">
-        <v>17.59</v>
+        <v>13</v>
       </c>
       <c r="K19" t="n">
-        <v>12.3</v>
+        <v>91.7</v>
       </c>
       <c r="L19" t="n">
-        <v>12.3</v>
+        <v>91.7</v>
       </c>
       <c r="M19" t="n">
-        <v>96</v>
+        <v>75.2</v>
       </c>
       <c r="N19" t="n">
-        <v>21.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>20.9</v>
+        <v>97.5</v>
       </c>
       <c r="P19" t="n">
-        <v>99</v>
+        <v>84.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>34.5</v>
+        <v>90.8</v>
       </c>
       <c r="R19" t="n">
-        <v>46.5</v>
+        <v>99.8</v>
       </c>
       <c r="S19" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T19" t="n">
-        <v>63.4</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>41.6</v>
+        <v>11.5</v>
       </c>
       <c r="V19" t="n">
-        <v>293168</v>
+        <v>59502</v>
       </c>
       <c r="W19" t="n">
-        <v>152549</v>
+        <v>10543</v>
       </c>
       <c r="X19" t="n">
-        <v>1.92</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="20">
       <c r="G20" t="inlineStr">
         <is>
-          <t>colmap</t>
+          <t>mast3r_ga</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.98</v>
+        <v>3.48</v>
       </c>
       <c r="I20" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="J20" t="n">
-        <v>11.59</v>
+        <v>16.84</v>
       </c>
       <c r="K20" t="n">
-        <v>96.59999999999999</v>
+        <v>44.5</v>
       </c>
       <c r="L20" t="n">
-        <v>96.59999999999999</v>
+        <v>44.5</v>
       </c>
       <c r="M20" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="N20" s="7" t="n">
-        <v>89.2</v>
+        <v>88.8</v>
+      </c>
+      <c r="N20" t="n">
+        <v>59.3</v>
       </c>
       <c r="O20" t="n">
-        <v>99.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="P20" t="n">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="Q20" s="7" t="n">
-        <v>95</v>
+        <v>96.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>77.2</v>
       </c>
       <c r="R20" t="n">
-        <v>99.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="S20" t="n">
-        <v>98</v>
-      </c>
-      <c r="T20" s="7" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="T20" t="n">
+        <v>93.3</v>
       </c>
       <c r="U20" t="n">
-        <v>9.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="V20" t="n">
-        <v>133185</v>
+        <v>177102</v>
       </c>
       <c r="W20" t="n">
-        <v>18583</v>
+        <v>46577</v>
       </c>
       <c r="X20" t="n">
-        <v>7.17</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="21">
       <c r="G21" t="inlineStr">
         <is>
-          <t>hloc_colmap</t>
+          <t>vggt</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.05</v>
+        <v>10.66</v>
       </c>
       <c r="I21" t="n">
-        <v>1.65</v>
+        <v>1.17</v>
       </c>
       <c r="J21" t="n">
-        <v>13</v>
+        <v>17.59</v>
       </c>
       <c r="K21" t="n">
-        <v>91.7</v>
+        <v>12.3</v>
       </c>
       <c r="L21" t="n">
-        <v>91.7</v>
+        <v>12.3</v>
       </c>
       <c r="M21" t="n">
-        <v>75.2</v>
+        <v>96</v>
       </c>
       <c r="N21" t="n">
-        <v>82.59999999999999</v>
+        <v>21.8</v>
       </c>
       <c r="O21" t="n">
-        <v>97.5</v>
+        <v>20.9</v>
       </c>
       <c r="P21" t="n">
-        <v>84.8</v>
+        <v>99</v>
       </c>
       <c r="Q21" t="n">
-        <v>90.8</v>
+        <v>34.5</v>
       </c>
       <c r="R21" t="n">
-        <v>99.8</v>
+        <v>46.5</v>
       </c>
       <c r="S21" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="T21" t="n">
-        <v>94.09999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="U21" t="n">
-        <v>11.5</v>
+        <v>41.6</v>
       </c>
       <c r="V21" t="n">
-        <v>59502</v>
+        <v>293168</v>
       </c>
       <c r="W21" t="n">
-        <v>10543</v>
+        <v>152549</v>
       </c>
       <c r="X21" t="n">
-        <v>5.64</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="22">
@@ -1953,66 +1953,66 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>mast3r_ga</t>
+          <t>colmap</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>8.31</v>
+        <v>2.49</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.3</v>
+        <v>1.88</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>17.87</v>
+        <v>17.77</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>28.6</v>
+        <v>58.8</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>28.6</v>
+        <v>58.8</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v>42.6</v>
+        <v>78.40000000000001</v>
+      </c>
+      <c r="N22" s="7" t="n">
+        <v>67.2</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>40.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>95.09999999999999</v>
-      </c>
-      <c r="Q22" s="4" t="n">
-        <v>57.1</v>
+        <v>95.2</v>
+      </c>
+      <c r="Q22" s="7" t="n">
+        <v>84.90000000000001</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>53.6</v>
+        <v>89.5</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="T22" s="4" t="n">
-        <v>69.8</v>
+        <v>99.8</v>
+      </c>
+      <c r="T22" s="7" t="n">
+        <v>94.40000000000001</v>
       </c>
       <c r="U22" s="4" t="n">
         <v>27.2</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>569403</v>
+        <v>327676</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>130311</v>
+        <v>29266</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>4.37</v>
+        <v>11.2</v>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
           <t>no DBSCAN</t>
         </is>
       </c>
-      <c r="Z22" s="6" t="inlineStr">
+      <c r="Z22" s="5" t="inlineStr">
         <is>
           <t>full reference</t>
         </is>
@@ -2021,175 +2021,175 @@
     <row r="23">
       <c r="G23" t="inlineStr">
         <is>
-          <t>vggt</t>
+          <t>hloc_colmap</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4.5</v>
+        <v>2.78</v>
       </c>
       <c r="I23" t="n">
-        <v>0.58</v>
+        <v>2.16</v>
       </c>
       <c r="J23" t="n">
-        <v>18.17</v>
+        <v>16.59</v>
       </c>
       <c r="K23" t="n">
-        <v>35.5</v>
+        <v>52.7</v>
       </c>
       <c r="L23" t="n">
-        <v>35.5</v>
+        <v>52.7</v>
       </c>
       <c r="M23" t="n">
-        <v>99.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="N23" t="n">
-        <v>52.4</v>
+        <v>58</v>
       </c>
       <c r="O23" t="n">
-        <v>54</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="Q23" t="n">
-        <v>70.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="R23" t="n">
-        <v>80.90000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="T23" t="n">
-        <v>89.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>37</v>
+        <v>34.9</v>
       </c>
       <c r="V23" t="n">
-        <v>2881563</v>
+        <v>261293</v>
       </c>
       <c r="W23" t="n">
-        <v>322936</v>
+        <v>23147</v>
       </c>
       <c r="X23" t="n">
-        <v>8.92</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="24">
       <c r="G24" t="inlineStr">
         <is>
-          <t>colmap</t>
+          <t>mast3r_ga</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2.49</v>
+        <v>8.31</v>
       </c>
       <c r="I24" t="n">
-        <v>1.88</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
-        <v>17.77</v>
+        <v>17.87</v>
       </c>
       <c r="K24" t="n">
-        <v>58.8</v>
+        <v>28.6</v>
       </c>
       <c r="L24" t="n">
-        <v>58.8</v>
+        <v>28.6</v>
       </c>
       <c r="M24" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="N24" s="7" t="n">
-        <v>67.2</v>
+        <v>83.3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>42.6</v>
       </c>
       <c r="O24" t="n">
-        <v>76.59999999999999</v>
+        <v>40.8</v>
       </c>
       <c r="P24" t="n">
-        <v>95.2</v>
-      </c>
-      <c r="Q24" s="7" t="n">
-        <v>84.90000000000001</v>
+        <v>95.09999999999999</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>57.1</v>
       </c>
       <c r="R24" t="n">
-        <v>89.5</v>
+        <v>53.6</v>
       </c>
       <c r="S24" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="T24" s="7" t="n">
-        <v>94.40000000000001</v>
+        <v>100</v>
+      </c>
+      <c r="T24" t="n">
+        <v>69.8</v>
       </c>
       <c r="U24" t="n">
         <v>27.2</v>
       </c>
       <c r="V24" t="n">
-        <v>327676</v>
+        <v>569403</v>
       </c>
       <c r="W24" t="n">
-        <v>29266</v>
+        <v>130311</v>
       </c>
       <c r="X24" t="n">
-        <v>11.2</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="25">
       <c r="G25" t="inlineStr">
         <is>
-          <t>hloc_colmap</t>
+          <t>vggt</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2.78</v>
+        <v>4.5</v>
       </c>
       <c r="I25" t="n">
-        <v>2.16</v>
+        <v>0.58</v>
       </c>
       <c r="J25" t="n">
-        <v>16.59</v>
+        <v>18.17</v>
       </c>
       <c r="K25" t="n">
-        <v>52.7</v>
+        <v>35.5</v>
       </c>
       <c r="L25" t="n">
-        <v>52.7</v>
+        <v>35.5</v>
       </c>
       <c r="M25" t="n">
-        <v>64.3</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>58</v>
+        <v>52.4</v>
       </c>
       <c r="O25" t="n">
-        <v>73.40000000000001</v>
+        <v>54</v>
       </c>
       <c r="P25" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="Q25" t="n">
-        <v>79.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="R25" t="n">
-        <v>86.90000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="T25" t="n">
-        <v>92.90000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>34.9</v>
+        <v>37</v>
       </c>
       <c r="V25" t="n">
-        <v>261293</v>
+        <v>2881563</v>
       </c>
       <c r="W25" t="n">
-        <v>23147</v>
+        <v>322936</v>
       </c>
       <c r="X25" t="n">
-        <v>11.29</v>
+        <v>8.92</v>
       </c>
     </row>
   </sheetData>
